--- a/r4-core-102-Krankenanstaltennummer-identifier-is-missing-R4-HL7®-AT-Core-Organization-Profile/StructureDefinition-at-core-practitioner.xlsx
+++ b/r4-core-102-Krankenanstaltennummer-identifier-is-missing-R4-HL7®-AT-Core-Organization-Profile/StructureDefinition-at-core-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-22T14:29:33+00:00</t>
+    <t>2024-10-30T16:15:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
